--- a/Codes_PFAS_models/PFAS_PBK_lifetime/scenario_iv_pfoa.xlsx
+++ b/Codes_PFAS_models/PFAS_PBK_lifetime/scenario_iv_pfoa.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jirka\Environment\PARC\WP7\Task7.3\Task 7.3.2\Complete_reverse_modelling_jan_2026\Model version for production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{97E6C55D-CFF7-40CA-A0C1-8E4EAB3076EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09203A4-F11E-461B-9EF6-3BDAC3E499BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PbkModelInstances" sheetId="1" r:id="rId1"/>
     <sheet name="PbkModelInstanceParameters" sheetId="2" r:id="rId2"/>
+    <sheet name="Readme" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PbkModelInstanceParameters!$A$1:$M$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PbkModelInstances!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="226">
   <si>
     <t>idModelInstance</t>
   </si>
@@ -71,24 +71,6 @@
     <t>PFOA</t>
   </si>
   <si>
-    <t>PFOS_Human_PARC_CS_Unc</t>
-  </si>
-  <si>
-    <t>PFOS</t>
-  </si>
-  <si>
-    <t>PFHxS_Human_PARC_CS_Unc</t>
-  </si>
-  <si>
-    <t>PFHxS</t>
-  </si>
-  <si>
-    <t>PFNA_Human_PARC_CS_Unc</t>
-  </si>
-  <si>
-    <t>PFNA</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -113,9 +95,6 @@
     <t>body weight</t>
   </si>
   <si>
-    <t>dimensionless</t>
-  </si>
-  <si>
     <t>QfilC</t>
   </si>
   <si>
@@ -167,24 +146,15 @@
     <t>Tmc</t>
   </si>
   <si>
-    <t>ug/d/kg^0.75</t>
-  </si>
-  <si>
     <t>Kt</t>
   </si>
   <si>
-    <t>ug/L</t>
-  </si>
-  <si>
     <t>resorption affinity</t>
   </si>
   <si>
     <t>kurinec</t>
   </si>
   <si>
-    <t>/d.kg^0.25</t>
-  </si>
-  <si>
     <t>urinary elimination rate constant</t>
   </si>
   <si>
@@ -476,9 +446,6 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>F, M</t>
   </si>
   <si>
@@ -500,7 +467,767 @@
     <t>maximum resorption rate, Klára put 19032 what is wrong since she forget she forced me to have there logsd instead of sd :(</t>
   </si>
   <si>
-    <t>partition coefficient lung/plasma, Klára put 1,21 what is wrong since she forget she forced me to have there logsd instead of sd :(</t>
+    <t>partition coefficient lung/plasma</t>
+  </si>
+  <si>
+    <t>age (in years) at day of plasma sampling</t>
+  </si>
+  <si>
+    <t>body height</t>
+  </si>
+  <si>
+    <t>start of modelled period</t>
+  </si>
+  <si>
+    <t>end of modelled period</t>
+  </si>
+  <si>
+    <t>modelling time step</t>
+  </si>
+  <si>
+    <t>duration of exposure</t>
+  </si>
+  <si>
+    <t>occupational exposure starting age (dermal and inhalation)</t>
+  </si>
+  <si>
+    <t>occupational exposure stopping age (dermal and inhalation)</t>
+  </si>
+  <si>
+    <t>age of menstruation start</t>
+  </si>
+  <si>
+    <t>age of menstruation end</t>
+  </si>
+  <si>
+    <t>body weight at birth</t>
+  </si>
+  <si>
+    <t>menstrual fluid volume</t>
+  </si>
+  <si>
+    <t>fractional skin storage</t>
+  </si>
+  <si>
+    <t>thickness of stratum corneum</t>
+  </si>
+  <si>
+    <t>thickness of viable epidermis</t>
+  </si>
+  <si>
+    <t>fraction of fat in stratum corneum</t>
+  </si>
+  <si>
+    <t>fraction of fat in viable epidermis</t>
+  </si>
+  <si>
+    <t>fraction of fat in epidermis</t>
+  </si>
+  <si>
+    <t>fraction of fat in blood</t>
+  </si>
+  <si>
+    <t>cell membrane partition kinetic constant</t>
+  </si>
+  <si>
+    <t>drink rate</t>
+  </si>
+  <si>
+    <t>partition coefficient for viable epidermis</t>
+  </si>
+  <si>
+    <t>ng/kg/d</t>
+  </si>
+  <si>
+    <t>oral exposure</t>
+  </si>
+  <si>
+    <t>partition coefficient for stratum corneum</t>
+  </si>
+  <si>
+    <t>for this model, dermal &amp; inhalation exposures are excluded</t>
+  </si>
+  <si>
+    <t>ng/L</t>
+  </si>
+  <si>
+    <t>ng/m^3</t>
+  </si>
+  <si>
+    <t>maternal milk concentration</t>
+  </si>
+  <si>
+    <t>placental transfer factor</t>
+  </si>
+  <si>
+    <t>ng</t>
+  </si>
+  <si>
+    <t>fecal clearance</t>
+  </si>
+  <si>
+    <t>drink concentration</t>
+  </si>
+  <si>
+    <t>amount of PFAS in arterial blood at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in venous blood at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in intestine at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in liver at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in adipose tissue at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in kidney at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in lungs at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in skin at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in rest of the body at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in filtrate at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in urine at birth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in urine between glomerular filtration and excretion at birth</t>
+  </si>
+  <si>
+    <t>maternal milk consumption</t>
+  </si>
+  <si>
+    <t>1/month</t>
+  </si>
+  <si>
+    <t>1/d.kg^0.25</t>
+  </si>
+  <si>
+    <t>μg/d/kg^0.75</t>
+  </si>
+  <si>
+    <t>μg/L</t>
+  </si>
+  <si>
+    <t>PBK modeling of PFASs with a probabilistic approach: Addressing  uncertainty in risk estimation</t>
+  </si>
+  <si>
+    <r>
+      <t>Jiří Kalina</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Jiří Komprda</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Daria Sapunova</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Carolina Vogs</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>2,3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Deepika Deepika</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>4,5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Vikas Kumar </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>4,5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Joost Westerhout</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Aude Ratier</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>7,8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Chrysanthi Pachoulide</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Johannes Kruisselbrink</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Jasper Engel</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Tony Fletcher</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Axel G. Andersson</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>,Pavel Piler</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Petr Šenk</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Klára Komprdová</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>1*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RECETOX, Faculty of Science, Masaryk University, Kotlarska 2, Brno, Czech Republic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Department of Animal Biosciences, Swedish University of Agricultural Science (SLU), Uppsala, Sweden</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Institute of Environmental Medicine, Karolinska Institutet, Stockholm, Sweden</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Institut de Recerca Biomèdica Catalunya Sud (IRBCatSud), Department of Chemical Engineering, Universitat Rovira i Virgili (URV), Tarragona, Spain</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> German Federal Institute for Risk Assessment (BfR), Department of Pesticides Safety, Max-Dohrn-Str. 8-10, 10589, Berlin, Germany</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212121"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> National Institute for Public Health and the Environment (RIVM), Center for Prevention, Lifestyle and Health, Bilthoven, Netherlands.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> INERIS, Unit of new approaches and models for Human health and environmental safety, Verneuil-en-Halatte, France </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> PériTox Laboratory, UMR-I 01 INERIS, Université de Picardie Jules Verne, Amiens, France</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Division of Toxicology, Wageningen University and Research, Wageningen, Netherlands</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF212121"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Mathematical &amp; Statistical Methods group (Biometris), Wageningen University &amp; Research, Droevendaalsesteeg 1, 6708 PB, Wageningen, The Netherlands</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>Department of Public Health, Environments &amp; Society, London School of Hygiene &amp; Tropical Medicine, London, UK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>School of Public Health and Community Medicine, Institute of Medicine, Sahlgrenska Academy, University of Gothenburg, Gothenburg, Sweden</t>
+    </r>
+  </si>
+  <si>
+    <t>This file scenario_iv_pfos.xlsx is used as parametrization of the lifeime PBK model (pfas_pbk_lifetime_model.R) It contains following lists:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PbkModelInstances</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> which contains a list of instances with following variables:</t>
+    </r>
+  </si>
+  <si>
+    <t>code of the model instance</t>
+  </si>
+  <si>
+    <t>code of the model</t>
+  </si>
+  <si>
+    <t>biological species</t>
+  </si>
+  <si>
+    <t>substance of the instance (PFOA or PFOS)</t>
+  </si>
+  <si>
+    <t>optional reference(s)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PbkModelInstanceParameters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> which contains a list of model parameters with following variables:</t>
+    </r>
+  </si>
+  <si>
+    <t>code of the model instance (if needed), empty cells are applicable on all instances</t>
+  </si>
+  <si>
+    <t>PFOS/PFOA</t>
+  </si>
+  <si>
+    <t>sex of the individual, "F" or "M"</t>
+  </si>
+  <si>
+    <t>name of the parameter as used in the model code</t>
+  </si>
+  <si>
+    <t>value in case of a deterministic input (not to be used)</t>
+  </si>
+  <si>
+    <t>physical unit of the parameter</t>
+  </si>
+  <si>
+    <t>name of a statisticl distribution (as in R language) used for the simulation</t>
+  </si>
+  <si>
+    <t>1st parameter of the statistical distribution (unique value in case of deterministic distribution, minimum in case of uniform or central value in case of other distributions)</t>
+  </si>
+  <si>
+    <t>2nd parameter of the statistical distribution (maximum in case of uniform, dispersion paramater in case of other distributions)</t>
+  </si>
+  <si>
+    <t>3rd parameter of the statistical distribution (minimum in case of truncated distributions)</t>
+  </si>
+  <si>
+    <t>4th parameter of the statistical distribution (maximum in case of truncated distributions)</t>
+  </si>
+  <si>
+    <t>detailed description of the parameter</t>
   </si>
 </sst>
 </file>
@@ -512,12 +1239,20 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,6 +1280,74 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -587,37 +1390,74 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -923,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -962,48 +1802,6 @@
       </c>
       <c r="D2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1022,10 +1820,11 @@
     <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="60.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="11" width="16" style="16" customWidth="1"/>
+    <col min="12" max="12" width="43" customWidth="1"/>
     <col min="13" max="13" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1034,37 +1833,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
@@ -1072,13 +1871,19 @@
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
+        <v>59</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1086,347 +1891,433 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F5" s="11"/>
       <c r="G5" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>118</v>
+        <v>60</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
       </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>118</v>
+        <v>61</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H7" s="2">
         <v>10950</v>
       </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>62</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>118</v>
+        <v>63</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2">
         <v>10950</v>
       </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>110</v>
+        <v>64</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
       </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>110</v>
+        <v>65</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>110</v>
+        <v>66</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2">
         <v>14</v>
       </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H13" s="2">
         <v>50</v>
       </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>68</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2">
         <v>3.68</v>
       </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3">
         <v>2.2889999999999998E-3</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="4">
         <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H16" s="2">
         <v>80</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="4">
         <v>13.2</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="4">
         <v>60</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="4">
         <v>100</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D17" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>119</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="4">
         <v>0.19500000000000001</v>
       </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
       <c r="L17" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>120</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="4">
         <v>0.14000000000000001</v>
       </c>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>121</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="4">
         <v>4.9000000000000002E-2</v>
       </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
       <c r="L19" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>122</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="L20" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="4">
         <v>4.9000000000000002E-2</v>
       </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
       <c r="L21" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>124</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="4">
         <v>0</v>
       </c>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
       <c r="L22" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>21</v>
+        <v>125</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="4">
         <v>0.1</v>
       </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
       <c r="L23" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1434,36 +2325,42 @@
         <v>5</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="F24" s="11">
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H24" s="2">
         <v>0.2</v>
       </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
       <c r="L24" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="F25" s="11">
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2">
         <v>0.44</v>
       </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
       <c r="L25" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1474,53 +2371,62 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>26</v>
+        <v>135</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H26" s="2">
         <v>4.2799999999999998E-2</v>
       </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
       <c r="L26" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="2">
+        <v>136</v>
+      </c>
+      <c r="F27" s="11">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H27" s="2">
         <v>0.39</v>
       </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
       <c r="L27" s="2" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F28" s="2">
+        <v>139</v>
+      </c>
+      <c r="F28" s="11">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H28" s="2">
         <v>0.61</v>
       </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
       <c r="L28" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1531,124 +2437,202 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H29" s="2">
         <v>0.1</v>
       </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
       <c r="L29" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H30" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H31" s="2">
         <v>1.5E-3</v>
       </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D32" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H32" s="2">
         <v>0.01</v>
       </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
+      </c>
+      <c r="F33" s="11">
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H33" s="2">
         <v>0.05</v>
       </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
+      </c>
+      <c r="F34" s="11">
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H34" s="2">
         <v>0.02</v>
       </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D35" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
+      </c>
+      <c r="F35" s="11">
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H35" s="2">
         <v>0.02</v>
       </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D36" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
+      </c>
+      <c r="F36" s="11">
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H36" s="2">
         <v>7.0000000000000001E-3</v>
       </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H37" s="2">
         <v>0.93</v>
       </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>77</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H38" s="2">
         <v>13</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1659,22 +2643,25 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>34</v>
+      <c r="F39" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H39" s="2">
         <v>414.07</v>
       </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
       <c r="L39" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1685,22 +2672,25 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>23</v>
+      <c r="F40" s="11">
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H40" s="2">
         <v>4.8099999999999996</v>
       </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1711,88 +2701,145 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>38</v>
+      <c r="F41" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H41" s="2">
         <v>2.34</v>
       </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
       <c r="L41" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D42" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
+      </c>
+      <c r="F42" s="11">
+        <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H42" s="2">
         <v>8.7999999999999998E-5</v>
       </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D43" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="F43" s="11">
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H43" s="2">
         <v>8.7999999999999998E-5</v>
       </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D44" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H44" s="2">
         <v>1.8699999999999999E-4</v>
       </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
       </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>169</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
       </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D47" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="2" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1803,29 +2850,29 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H48" s="2">
         <f>6600*24</f>
         <v>158400</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="4">
         <v>9.8538770519827938</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="14">
         <v>42480</v>
       </c>
-      <c r="K48" s="4">
+      <c r="K48" s="14">
         <v>312000</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1836,22 +2883,24 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>191</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H49" s="2">
         <v>55</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="4">
         <v>1.77</v>
       </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
       <c r="L49" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1862,58 +2911,61 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>189</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H50" s="5">
+        <v>115</v>
+      </c>
+      <c r="H50" s="4">
         <f>0.05*24</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="5">
         <f>0.017*24</f>
         <v>0.40800000000000003</v>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="6">
         <f>0.0003*24</f>
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="K50" s="8">
+      <c r="K50" s="7">
         <v>2.4239999999999999</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>119</v>
+        <v>84</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H51" s="9">
+        <v>115</v>
+      </c>
+      <c r="H51" s="8">
         <f>7.08333333333333E-07*24</f>
         <v>1.6999999999999993E-5</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="15">
         <f>6.1464486465505E-07*24</f>
         <v>1.4751476751721199E-5</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="15">
         <f>3.33333333333333E-07*24</f>
         <v>7.9999999999999912E-6</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="15">
         <f>1.70833333333333E-06*24</f>
         <v>4.0999999999999919E-5</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1924,28 +2976,28 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
+      </c>
+      <c r="F52" s="11">
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H52" s="2">
         <v>0.02</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52" s="4">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="4">
         <v>1E-3</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="4">
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1956,22 +3008,24 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="F53" s="11">
+        <v>1</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H53" s="2">
         <v>1.03</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53" s="4">
         <v>0.61</v>
       </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
       <c r="L53" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1982,22 +3036,24 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="F54" s="11">
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H54" s="2">
         <v>0.21</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54" s="4">
         <v>0.09</v>
       </c>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
       <c r="L54" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2008,22 +3064,24 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="F55" s="11">
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H55" s="2">
         <v>0.93</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="9">
         <v>0.17599999999999999</v>
       </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
       <c r="L55" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2034,22 +3092,24 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="F56" s="11">
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H56" s="2">
         <v>0.13</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I56" s="4">
         <v>1.4E-2</v>
       </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
       <c r="L56" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2060,22 +3120,24 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="F57" s="11">
+        <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H57" s="2">
         <v>0.11</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I57" s="4">
         <v>0.03</v>
       </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
       <c r="L57" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2086,22 +3148,24 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="F58" s="11">
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H58" s="2">
         <v>0.11</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I58" s="4">
         <v>0.05</v>
       </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2112,221 +3176,368 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
+      </c>
+      <c r="F59" s="11">
+        <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H59" s="2">
         <v>1.41</v>
       </c>
-      <c r="I59" s="2">
+      <c r="I59" s="4">
         <v>0.1906203596086497</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="4">
         <v>0.18</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K59" s="4">
         <v>9.08</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H60" s="2">
         <v>2</v>
       </c>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D61" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="F61" s="11">
+        <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H61" s="2">
         <v>0.74</v>
       </c>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D62" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="F62" s="11">
+        <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H62" s="2">
         <v>0.03</v>
       </c>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D63" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H63" s="2">
         <v>7.6999999999999999E-2</v>
       </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
       <c r="L63" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D64" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H64" s="2">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="65" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D65" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H65" s="2">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="66" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D66" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H66" s="2">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="67" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D67" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H67" s="2">
         <v>0.99929853000000002</v>
       </c>
-    </row>
-    <row r="68" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D68" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H68" s="2">
         <v>66.836076399999996</v>
       </c>
-    </row>
-    <row r="69" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D69" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H69" s="2">
         <v>10.000151000000001</v>
       </c>
-    </row>
-    <row r="70" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D70" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H70" s="2">
         <v>5.8857574599999998</v>
       </c>
-    </row>
-    <row r="71" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D71" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H71" s="2">
         <v>4.5199999999999996</v>
       </c>
-    </row>
-    <row r="72" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="72" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D72" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H72" s="2">
         <v>3.39</v>
       </c>
-    </row>
-    <row r="73" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="73" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D73" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H73" s="2">
         <v>74.910879199999997</v>
       </c>
-    </row>
-    <row r="74" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D74" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H74" s="2">
         <v>2.0960600000000001E-5</v>
       </c>
-    </row>
-    <row r="75" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D75" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H75" s="2">
         <v>42.279107140000001</v>
       </c>
-    </row>
-    <row r="76" spans="4:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D76" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H76" s="2">
         <v>769.13474940000003</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2336,10 +3547,270 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF4F731-874E-45FE-AA80-8B354D46C2CF}">
+  <dimension ref="B3:D46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="17"/>
+    </row>
+    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="23"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="24"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="24" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2481,26 +3952,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88C6B4-595B-49EB-BB0C-4EE3D841E4E8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4321C31B-FEA8-48E5-8044-B03A14F31655}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="552a4e32-e292-4e84-b79f-aefc699ca0de"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2524,9 +3984,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4321C31B-FEA8-48E5-8044-B03A14F31655}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88C6B4-595B-49EB-BB0C-4EE3D841E4E8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="552a4e32-e292-4e84-b79f-aefc699ca0de"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Codes_PFAS_models/PFAS_PBK_lifetime/scenario_iv_pfoa.xlsx
+++ b/Codes_PFAS_models/PFAS_PBK_lifetime/scenario_iv_pfoa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jirka\Environment\PARC\WP7\Task7.3\Task 7.3.2\Complete_reverse_modelling_jan_2026\Model version for production\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucnmuni-my.sharepoint.com/personal/150824_muni_cz/Documents/Soubory z chatu aplikace Microsoft Teams/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09203A4-F11E-461B-9EF6-3BDAC3E499BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{226E438E-9209-4A8B-9FA0-7127943309C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17610" yWindow="555" windowWidth="21045" windowHeight="19485" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PbkModelInstances" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,12 @@
     <t>PFOA</t>
   </si>
   <si>
+    <t>Compound</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -83,9 +89,33 @@
     <t>DistributionType</t>
   </si>
   <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>Param4</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>const</t>
+  </si>
+  <si>
+    <t>age (in years) at day of plasma sampling</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
@@ -95,33 +125,243 @@
     <t>body weight</t>
   </si>
   <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>body height</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>F, M</t>
+  </si>
+  <si>
+    <t>TSTART</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>start of modelled period</t>
+  </si>
+  <si>
+    <t>TSTOP</t>
+  </si>
+  <si>
+    <t>end of modelled period</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>modelling time step</t>
+  </si>
+  <si>
+    <t>exposure_duration</t>
+  </si>
+  <si>
+    <t>duration of exposure</t>
+  </si>
+  <si>
+    <t>age_start_occ_exp</t>
+  </si>
+  <si>
+    <t>occupational exposure starting age (dermal and inhalation)</t>
+  </si>
+  <si>
+    <t>age_stop_occ_exp</t>
+  </si>
+  <si>
+    <t>occupational exposure stopping age (dermal and inhalation)</t>
+  </si>
+  <si>
+    <t>age_start_menstruation</t>
+  </si>
+  <si>
+    <t>age of menstruation start</t>
+  </si>
+  <si>
+    <t>age_stop_menstruation</t>
+  </si>
+  <si>
+    <t>age of menstruation end</t>
+  </si>
+  <si>
+    <t>BWbirth</t>
+  </si>
+  <si>
+    <t>body weight at birth</t>
+  </si>
+  <si>
+    <t>MFV</t>
+  </si>
+  <si>
+    <t>L/d</t>
+  </si>
+  <si>
+    <t>norm</t>
+  </si>
+  <si>
+    <t>menstrual fluid volume</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>1/min</t>
+  </si>
+  <si>
+    <t>truncnorm</t>
+  </si>
+  <si>
+    <t>heart beat rate</t>
+  </si>
+  <si>
+    <t>SDLun</t>
+  </si>
+  <si>
+    <t>lnorm</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of lungs</t>
+  </si>
+  <si>
+    <t>SDK</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of kidney</t>
+  </si>
+  <si>
+    <t>SDInt</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of intestine</t>
+  </si>
+  <si>
+    <t>SDL</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of liver</t>
+  </si>
+  <si>
+    <t>SDSk</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of skin</t>
+  </si>
+  <si>
+    <t>SDAdi</t>
+  </si>
+  <si>
+    <t>SDB</t>
+  </si>
+  <si>
+    <t>added standard deviation of the weight of blood</t>
+  </si>
+  <si>
     <t>QfilC</t>
   </si>
   <si>
     <t>fraction of kidney plasma flow to filtrate</t>
   </si>
   <si>
+    <t>Htc</t>
+  </si>
+  <si>
+    <t>hematocrit</t>
+  </si>
+  <si>
+    <t>VplasC</t>
+  </si>
+  <si>
     <t>L/kg</t>
   </si>
   <si>
     <t>fraction plasma volume</t>
   </si>
   <si>
-    <t>Htc</t>
-  </si>
-  <si>
-    <t>hematocrit</t>
+    <t>VartC</t>
+  </si>
+  <si>
+    <t>fraction of arterial blood</t>
+  </si>
+  <si>
+    <t>VvenC</t>
+  </si>
+  <si>
+    <t>fraction of venous blood</t>
   </si>
   <si>
     <t>SkinThickness</t>
   </si>
   <si>
-    <t>cm</t>
-  </si>
-  <si>
     <t>skin thickness</t>
   </si>
   <si>
+    <t>fss</t>
+  </si>
+  <si>
+    <t>fractional skin storage</t>
+  </si>
+  <si>
+    <t>hsc</t>
+  </si>
+  <si>
+    <t>thickness of stratum corneum</t>
+  </si>
+  <si>
+    <t>hve</t>
+  </si>
+  <si>
+    <t>thickness of viable epidermis</t>
+  </si>
+  <si>
+    <t>ffatsc</t>
+  </si>
+  <si>
+    <t>fraction of fat in stratum corneum</t>
+  </si>
+  <si>
+    <t>ffatve</t>
+  </si>
+  <si>
+    <t>fraction of fat in viable epidermis</t>
+  </si>
+  <si>
+    <t>ffatepi</t>
+  </si>
+  <si>
+    <t>fraction of fat in epidermis</t>
+  </si>
+  <si>
+    <t>ffatbl</t>
+  </si>
+  <si>
+    <t>fraction of fat in blood</t>
+  </si>
+  <si>
+    <t>Kpcell</t>
+  </si>
+  <si>
+    <t>cm/h</t>
+  </si>
+  <si>
+    <t>cell membrane partition kinetic constant</t>
+  </si>
+  <si>
+    <t>Drinkrate</t>
+  </si>
+  <si>
+    <t>mL/kg/d</t>
+  </si>
+  <si>
+    <t>drink rate</t>
+  </si>
+  <si>
     <t>MW</t>
   </si>
   <si>
@@ -143,21 +383,87 @@
     <t>vapor pressure</t>
   </si>
   <si>
+    <t>Kpve</t>
+  </si>
+  <si>
+    <t>partition coefficient for viable epidermis</t>
+  </si>
+  <si>
+    <t>Kpsc</t>
+  </si>
+  <si>
+    <t>partition coefficient for stratum corneum</t>
+  </si>
+  <si>
+    <t>Oralexpo</t>
+  </si>
+  <si>
+    <t>ng/kg/d</t>
+  </si>
+  <si>
+    <t>oral exposure</t>
+  </si>
+  <si>
+    <t>Drinkconc</t>
+  </si>
+  <si>
+    <t>ng/L</t>
+  </si>
+  <si>
+    <t>drink concentration</t>
+  </si>
+  <si>
+    <t>Cinh</t>
+  </si>
+  <si>
+    <t>ng/m^3</t>
+  </si>
+  <si>
+    <t>for this model, dermal &amp; inhalation exposures are excluded</t>
+  </si>
+  <si>
+    <t>Cdermal</t>
+  </si>
+  <si>
     <t>Tmc</t>
   </si>
   <si>
+    <t>μg/d/kg^0.75</t>
+  </si>
+  <si>
+    <t>trunclnorm</t>
+  </si>
+  <si>
+    <t>maximum resorption rate</t>
+  </si>
+  <si>
     <t>Kt</t>
   </si>
   <si>
+    <t>μg/L</t>
+  </si>
+  <si>
     <t>resorption affinity</t>
   </si>
   <si>
     <t>kurinec</t>
   </si>
   <si>
+    <t>1/d.kg^0.25</t>
+  </si>
+  <si>
     <t>urinary elimination rate constant</t>
   </si>
   <si>
+    <t>CLfaeces</t>
+  </si>
+  <si>
+    <t>L/kg/d</t>
+  </si>
+  <si>
+    <t>fecal clearance</t>
+  </si>
+  <si>
     <t>Free</t>
   </si>
   <si>
@@ -203,421 +509,115 @@
     <t>PLun</t>
   </si>
   <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>Param3</t>
-  </si>
-  <si>
-    <t>Param4</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Compound</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>TSTART</t>
-  </si>
-  <si>
-    <t>TSTOP</t>
-  </si>
-  <si>
-    <t>DT</t>
-  </si>
-  <si>
-    <t>exposure_duration</t>
-  </si>
-  <si>
-    <t>age_start_occ_exp</t>
-  </si>
-  <si>
-    <t>age_stop_occ_exp</t>
-  </si>
-  <si>
-    <t>age_start_menstruation</t>
-  </si>
-  <si>
-    <t>age_stop_menstruation</t>
-  </si>
-  <si>
-    <t>BWbirth</t>
-  </si>
-  <si>
-    <t>fss</t>
-  </si>
-  <si>
-    <t>hsc</t>
-  </si>
-  <si>
-    <t>hve</t>
-  </si>
-  <si>
-    <t>ffatsc</t>
-  </si>
-  <si>
-    <t>ffatve</t>
-  </si>
-  <si>
-    <t>ffatepi</t>
-  </si>
-  <si>
-    <t>ffatbl</t>
-  </si>
-  <si>
-    <t>Kpcell</t>
-  </si>
-  <si>
-    <t>Drinkrate</t>
-  </si>
-  <si>
-    <t>Kpsc</t>
-  </si>
-  <si>
-    <t>Kpve</t>
-  </si>
-  <si>
-    <t>Oralexpo</t>
-  </si>
-  <si>
-    <t>Drinkconc</t>
-  </si>
-  <si>
-    <t>Cinh</t>
-  </si>
-  <si>
-    <t>Cdermal</t>
-  </si>
-  <si>
-    <t>CLfaeces</t>
+    <t>partition coefficient lung/plasma</t>
   </si>
   <si>
     <t>maternal</t>
   </si>
   <si>
+    <t>maternal milk concentration</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
+    <t>placental transfer factor</t>
+  </si>
+  <si>
     <t>Ratio</t>
   </si>
   <si>
+    <t>milk concentration/maternal serum concentration during breastfeeding</t>
+  </si>
+  <si>
     <t>DECLINE</t>
   </si>
   <si>
+    <t>1/month</t>
+  </si>
+  <si>
+    <t>decline of concentration in milk was 7.7% per month</t>
+  </si>
+  <si>
     <t>Milkconsumption</t>
   </si>
   <si>
+    <t>maternal milk consumption</t>
+  </si>
+  <si>
+    <t>Aartbirth</t>
+  </si>
+  <si>
+    <t>ng</t>
+  </si>
+  <si>
+    <t>amount of PFAS in arterial blood at birth</t>
+  </si>
+  <si>
+    <t>Avenbirth</t>
+  </si>
+  <si>
+    <t>amount of PFAS in venous blood at birth</t>
+  </si>
+  <si>
     <t>AGbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in intestine at birth</t>
+  </si>
+  <si>
     <t>ALbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in liver at birth</t>
+  </si>
+  <si>
     <t>AFbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in adipose tissue at birth</t>
+  </si>
+  <si>
     <t>AKbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in kidney at birth</t>
+  </si>
+  <si>
     <t>ALunbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in lungs at birth</t>
+  </si>
+  <si>
     <t>ASkbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in skin at birth</t>
+  </si>
+  <si>
     <t>ARbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in rest of the body at birth</t>
+  </si>
+  <si>
     <t>Afilbirth</t>
   </si>
   <si>
+    <t>amount of PFAS in filtrate at birth</t>
+  </si>
+  <si>
     <t>Adelaybirth</t>
   </si>
   <si>
+    <t>amount of PFAS in urine between glomerular filtration and excretion at birth</t>
+  </si>
+  <si>
     <t>Aurinebirth</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>cm/h</t>
-  </si>
-  <si>
-    <t>mL/kg/d</t>
-  </si>
-  <si>
-    <t>const</t>
-  </si>
-  <si>
-    <t>milk concentration/maternal serum concentration during breastfeeding, new add opinion 2020</t>
-  </si>
-  <si>
-    <t>decline of concentration in milk was 7.7% per month, new add opinion 2020</t>
-  </si>
-  <si>
-    <t>MFV</t>
-  </si>
-  <si>
-    <t>L/d</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>L/kg/d</t>
-  </si>
-  <si>
-    <t>Aartbirth</t>
-  </si>
-  <si>
-    <t>Avenbirth</t>
-  </si>
-  <si>
-    <t>lnorm</t>
-  </si>
-  <si>
-    <t>trunclnorm</t>
-  </si>
-  <si>
-    <t>norm</t>
-  </si>
-  <si>
-    <t>truncnorm</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>heart beat rate</t>
-  </si>
-  <si>
-    <t>1/min</t>
-  </si>
-  <si>
-    <t>SDLun</t>
-  </si>
-  <si>
-    <t>SDK</t>
-  </si>
-  <si>
-    <t>SDInt</t>
-  </si>
-  <si>
-    <t>SDL</t>
-  </si>
-  <si>
-    <t>SDSk</t>
-  </si>
-  <si>
-    <t>SDAdi</t>
-  </si>
-  <si>
-    <t>SDB</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of lungs (by Bosgra)</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of kidney (by Bosgra)</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of intestine (by Bosgra)</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of liver (by Bosgra)</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of skin (by Bosgra)</t>
-  </si>
-  <si>
-    <t>added standard deviation of the weight of blood (by Bosgra)</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>F, M</t>
-  </si>
-  <si>
-    <t>VplasC</t>
-  </si>
-  <si>
-    <t>VartC</t>
-  </si>
-  <si>
-    <t>fraction of arterial blood</t>
-  </si>
-  <si>
-    <t>fraction of venous blood</t>
-  </si>
-  <si>
-    <t>VvenC</t>
-  </si>
-  <si>
-    <t>maximum resorption rate, Klára put 19032 what is wrong since she forget she forced me to have there logsd instead of sd :(</t>
-  </si>
-  <si>
-    <t>partition coefficient lung/plasma</t>
-  </si>
-  <si>
-    <t>age (in years) at day of plasma sampling</t>
-  </si>
-  <si>
-    <t>body height</t>
-  </si>
-  <si>
-    <t>start of modelled period</t>
-  </si>
-  <si>
-    <t>end of modelled period</t>
-  </si>
-  <si>
-    <t>modelling time step</t>
-  </si>
-  <si>
-    <t>duration of exposure</t>
-  </si>
-  <si>
-    <t>occupational exposure starting age (dermal and inhalation)</t>
-  </si>
-  <si>
-    <t>occupational exposure stopping age (dermal and inhalation)</t>
-  </si>
-  <si>
-    <t>age of menstruation start</t>
-  </si>
-  <si>
-    <t>age of menstruation end</t>
-  </si>
-  <si>
-    <t>body weight at birth</t>
-  </si>
-  <si>
-    <t>menstrual fluid volume</t>
-  </si>
-  <si>
-    <t>fractional skin storage</t>
-  </si>
-  <si>
-    <t>thickness of stratum corneum</t>
-  </si>
-  <si>
-    <t>thickness of viable epidermis</t>
-  </si>
-  <si>
-    <t>fraction of fat in stratum corneum</t>
-  </si>
-  <si>
-    <t>fraction of fat in viable epidermis</t>
-  </si>
-  <si>
-    <t>fraction of fat in epidermis</t>
-  </si>
-  <si>
-    <t>fraction of fat in blood</t>
-  </si>
-  <si>
-    <t>cell membrane partition kinetic constant</t>
-  </si>
-  <si>
-    <t>drink rate</t>
-  </si>
-  <si>
-    <t>partition coefficient for viable epidermis</t>
-  </si>
-  <si>
-    <t>ng/kg/d</t>
-  </si>
-  <si>
-    <t>oral exposure</t>
-  </si>
-  <si>
-    <t>partition coefficient for stratum corneum</t>
-  </si>
-  <si>
-    <t>for this model, dermal &amp; inhalation exposures are excluded</t>
-  </si>
-  <si>
-    <t>ng/L</t>
-  </si>
-  <si>
-    <t>ng/m^3</t>
-  </si>
-  <si>
-    <t>maternal milk concentration</t>
-  </si>
-  <si>
-    <t>placental transfer factor</t>
-  </si>
-  <si>
-    <t>ng</t>
-  </si>
-  <si>
-    <t>fecal clearance</t>
-  </si>
-  <si>
-    <t>drink concentration</t>
-  </si>
-  <si>
-    <t>amount of PFAS in arterial blood at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in venous blood at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in intestine at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in liver at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in adipose tissue at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in kidney at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in lungs at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in skin at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in rest of the body at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in filtrate at birth</t>
-  </si>
-  <si>
     <t>amount of PFAS in urine at birth</t>
-  </si>
-  <si>
-    <t>amount of PFAS in urine between glomerular filtration and excretion at birth</t>
-  </si>
-  <si>
-    <t>maternal milk consumption</t>
-  </si>
-  <si>
-    <t>1/month</t>
-  </si>
-  <si>
-    <t>1/d.kg^0.25</t>
-  </si>
-  <si>
-    <t>μg/d/kg^0.75</t>
-  </si>
-  <si>
-    <t>μg/L</t>
   </si>
   <si>
     <t>PBK modeling of PFASs with a probabilistic approach: Addressing  uncertainty in risk estimation</t>
@@ -1200,7 +1200,7 @@
     <t>PFOS/PFOA</t>
   </si>
   <si>
-    <t>sex of the individual, "F" or "M"</t>
+    <t>sex of the individual, "F" or "M" (optional)</t>
   </si>
   <si>
     <t>name of the parameter as used in the model code</t>
@@ -1239,7 +1239,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1427,9 +1427,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1458,6 +1455,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -1764,7 +1764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
@@ -1773,7 +1773,7 @@
     <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1813,7 +1813,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -1823,130 +1823,130 @@
     <col min="6" max="6" width="14" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="11" width="16" style="16" customWidth="1"/>
+    <col min="9" max="11" width="16" style="15" customWidth="1"/>
     <col min="12" max="12" width="43" customWidth="1"/>
     <col min="13" max="13" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="2" customFormat="1">
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1">
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1">
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="2" customFormat="1">
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1955,18 +1955,18 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1">
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2">
         <v>10950</v>
@@ -1975,18 +1975,18 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1">
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1995,18 +1995,18 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="2" customFormat="1">
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2">
         <v>10950</v>
@@ -2015,18 +2015,18 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="2" customFormat="1">
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -2035,18 +2035,18 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="2" customFormat="1">
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -2055,18 +2055,18 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="2" customFormat="1">
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2">
         <v>14</v>
@@ -2075,18 +2075,18 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="2" customFormat="1">
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2">
         <v>50</v>
@@ -2095,18 +2095,18 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1">
       <c r="D14" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2">
         <v>3.68</v>
@@ -2115,18 +2115,18 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="2" customFormat="1">
       <c r="D15" s="2" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="H15" s="3">
         <v>2.2889999999999998E-3</v>
@@ -2137,18 +2137,18 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="2" customFormat="1">
       <c r="D16" s="2" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H16" s="2">
         <v>80</v>
@@ -2163,18 +2163,18 @@
         <v>100</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1">
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -2185,18 +2185,18 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1">
       <c r="D18" s="2" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2207,18 +2207,18 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1">
       <c r="D19" s="2" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -2229,18 +2229,18 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1">
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2251,18 +2251,18 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1">
       <c r="D21" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2273,18 +2273,18 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1">
       <c r="D22" s="2" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2295,18 +2295,18 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1">
       <c r="D23" s="2" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2317,21 +2317,21 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1">
       <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F24" s="11">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H24" s="2">
         <v>0.2</v>
@@ -2340,18 +2340,18 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1">
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="F25" s="11">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H25" s="2">
         <v>0.44</v>
@@ -2360,10 +2360,10 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -2371,13 +2371,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H26" s="2">
         <v>4.2799999999999998E-2</v>
@@ -2386,18 +2386,18 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1">
       <c r="D27" s="2" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="F27" s="11">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H27" s="2">
         <v>0.39</v>
@@ -2406,18 +2406,18 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1">
       <c r="D28" s="2" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="F28" s="11">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2">
         <v>0.61</v>
@@ -2426,10 +2426,10 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1">
       <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
@@ -2437,13 +2437,13 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H29" s="2">
         <v>0.1</v>
@@ -2452,18 +2452,18 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1">
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H30" s="2">
         <v>5.0000000000000001E-3</v>
@@ -2472,18 +2472,18 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1">
       <c r="D31" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H31" s="2">
         <v>1.5E-3</v>
@@ -2492,18 +2492,18 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1">
       <c r="D32" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H32" s="2">
         <v>0.01</v>
@@ -2512,18 +2512,18 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1">
       <c r="D33" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F33" s="11">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H33" s="2">
         <v>0.05</v>
@@ -2532,18 +2532,18 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1">
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F34" s="11">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H34" s="2">
         <v>0.02</v>
@@ -2552,18 +2552,18 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1">
       <c r="D35" s="2" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F35" s="11">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2">
         <v>0.02</v>
@@ -2572,18 +2572,18 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1">
       <c r="D36" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="F36" s="11">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H36" s="2">
         <v>7.0000000000000001E-3</v>
@@ -2592,18 +2592,18 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1">
       <c r="D37" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>101</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H37" s="2">
         <v>0.93</v>
@@ -2612,18 +2612,18 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1">
       <c r="D38" s="2" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H38" s="2">
         <v>13</v>
@@ -2632,10 +2632,10 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="2" customFormat="1">
       <c r="A39" s="2" t="s">
         <v>5</v>
       </c>
@@ -2643,16 +2643,16 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H39" s="2">
         <v>414.07</v>
@@ -2661,10 +2661,10 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>8</v>
@@ -2681,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H40" s="2">
         <v>4.8099999999999996</v>
@@ -2690,10 +2690,10 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1">
       <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
@@ -2701,16 +2701,16 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H41" s="2">
         <v>2.34</v>
@@ -2719,18 +2719,18 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="2" customFormat="1">
       <c r="D42" s="2" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="F42" s="11">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H42" s="2">
         <v>8.7999999999999998E-5</v>
@@ -2739,18 +2739,18 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1">
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F43" s="11">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H43" s="2">
         <v>8.7999999999999998E-5</v>
@@ -2759,18 +2759,18 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="2" customFormat="1">
       <c r="D44" s="2" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H44" s="2">
         <v>1.8699999999999999E-4</v>
@@ -2779,18 +2779,18 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="2" customFormat="1">
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2799,18 +2799,18 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="2" customFormat="1">
       <c r="D46" s="2" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2819,18 +2819,18 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="2" customFormat="1">
       <c r="D47" s="2" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -2839,10 +2839,10 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="2" customFormat="1">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -2850,32 +2850,31 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H48" s="2">
-        <f>6600*24</f>
-        <v>158400</v>
+        <v>115200</v>
       </c>
       <c r="I48" s="4">
-        <v>9.8538770519827938</v>
-      </c>
-      <c r="J48" s="14">
+        <v>0.32</v>
+      </c>
+      <c r="J48" s="24">
         <v>42480</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K48" s="24">
         <v>312000</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="2" customFormat="1">
       <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
@@ -2883,13 +2882,13 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="H49" s="2">
         <v>55</v>
@@ -2900,10 +2899,10 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="2" customFormat="1">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -2911,13 +2910,13 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H50" s="4">
         <f>0.05*24</f>
@@ -2935,40 +2934,40 @@
         <v>2.4239999999999999</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="2" customFormat="1">
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H51" s="8">
-        <f>7.08333333333333E-07*24</f>
-        <v>1.6999999999999993E-5</v>
-      </c>
-      <c r="I51" s="15">
-        <f>6.1464486465505E-07*24</f>
-        <v>1.4751476751721199E-5</v>
-      </c>
-      <c r="J51" s="15">
+        <f>0.000000455567*24</f>
+        <v>1.0933608E-5</v>
+      </c>
+      <c r="I51" s="14">
+        <f>0.00000017155*24</f>
+        <v>4.1172000000000002E-6</v>
+      </c>
+      <c r="J51" s="14">
         <f>3.33333333333333E-07*24</f>
         <v>7.9999999999999912E-6</v>
       </c>
-      <c r="K51" s="15">
+      <c r="K51" s="14">
         <f>1.70833333333333E-06*24</f>
         <v>4.0999999999999919E-5</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="2" customFormat="1">
       <c r="A52" s="2" t="s">
         <v>5</v>
       </c>
@@ -2976,16 +2975,16 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="F52" s="11">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H52" s="2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I52" s="4">
         <v>3.0000000000000001E-3</v>
@@ -2997,10 +2996,10 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="2" customFormat="1">
       <c r="A53" s="2" t="s">
         <v>5</v>
       </c>
@@ -3008,27 +3007,27 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="F53" s="11">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H53" s="2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="I53" s="4">
-        <v>0.61</v>
+        <v>0.12</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="2" customFormat="1">
       <c r="A54" s="2" t="s">
         <v>5</v>
       </c>
@@ -3036,27 +3035,27 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="F54" s="11">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H54" s="2">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="I54" s="4">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="2" customFormat="1">
       <c r="A55" s="2" t="s">
         <v>5</v>
       </c>
@@ -3064,27 +3063,27 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="F55" s="11">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H55" s="2">
-        <v>0.93</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I55" s="9">
-        <v>0.17599999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="2" customFormat="1">
       <c r="A56" s="2" t="s">
         <v>5</v>
       </c>
@@ -3092,27 +3091,27 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="F56" s="11">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H56" s="2">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I56" s="4">
-        <v>1.4E-2</v>
+        <v>0.01</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="2" customFormat="1">
       <c r="A57" s="2" t="s">
         <v>5</v>
       </c>
@@ -3120,13 +3119,13 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="F57" s="11">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H57" s="2">
         <v>0.11</v>
@@ -3137,10 +3136,10 @@
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="2" customFormat="1">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -3148,27 +3147,27 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="F58" s="11">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H58" s="2">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="I58" s="4">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="2" customFormat="1">
       <c r="A59" s="2" t="s">
         <v>5</v>
       </c>
@@ -3176,19 +3175,19 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="F59" s="11">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H59" s="2">
-        <v>1.41</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="I59" s="4">
-        <v>0.1906203596086497</v>
+        <v>0.25</v>
       </c>
       <c r="J59" s="4">
         <v>0.18</v>
@@ -3197,18 +3196,18 @@
         <v>9.08</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="2" customFormat="1">
       <c r="D60" s="2" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H60" s="2">
         <v>2</v>
@@ -3217,18 +3216,18 @@
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="2" customFormat="1">
       <c r="D61" s="2" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="F61" s="11">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H61" s="2">
         <v>0.74</v>
@@ -3237,18 +3236,18 @@
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
       <c r="L61" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="2" customFormat="1">
       <c r="D62" s="2" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="F62" s="11">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H62" s="2">
         <v>0.03</v>
@@ -3257,18 +3256,18 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="2" customFormat="1">
       <c r="D63" s="2" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H63" s="2">
         <v>7.6999999999999999E-2</v>
@@ -3277,18 +3276,18 @@
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="2" customFormat="1">
       <c r="D64" s="2" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H64" s="2">
         <v>0.8</v>
@@ -3297,18 +3296,18 @@
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="65" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12" s="2" customFormat="1">
       <c r="D65" s="2" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H65" s="2">
         <v>0.39</v>
@@ -3317,18 +3316,18 @@
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
       <c r="L65" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="66" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12" s="2" customFormat="1">
       <c r="D66" s="2" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H66" s="2">
         <v>0.61</v>
@@ -3337,18 +3336,18 @@
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="67" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12" s="2" customFormat="1">
       <c r="D67" s="2" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H67" s="2">
         <v>0.99929853000000002</v>
@@ -3357,18 +3356,18 @@
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="68" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12" s="2" customFormat="1">
       <c r="D68" s="2" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H68" s="2">
         <v>66.836076399999996</v>
@@ -3377,18 +3376,18 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="69" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="4:12" s="2" customFormat="1">
       <c r="D69" s="2" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H69" s="2">
         <v>10.000151000000001</v>
@@ -3397,18 +3396,18 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="70" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" spans="4:12" s="2" customFormat="1">
       <c r="D70" s="2" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H70" s="2">
         <v>5.8857574599999998</v>
@@ -3417,18 +3416,18 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" spans="4:12" s="2" customFormat="1">
+      <c r="D71" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="71" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F71" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H71" s="2">
         <v>4.5199999999999996</v>
@@ -3440,15 +3439,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:12" s="2" customFormat="1">
       <c r="D72" s="2" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H72" s="2">
         <v>3.39</v>
@@ -3457,18 +3456,18 @@
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="73" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" spans="4:12" s="2" customFormat="1">
       <c r="D73" s="2" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H73" s="2">
         <v>74.910879199999997</v>
@@ -3477,18 +3476,18 @@
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
       <c r="L73" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="74" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="74" spans="4:12" s="2" customFormat="1">
       <c r="D74" s="2" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H74" s="2">
         <v>2.0960600000000001E-5</v>
@@ -3497,18 +3496,18 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="75" spans="4:12" s="2" customFormat="1">
       <c r="D75" s="2" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H75" s="2">
         <v>42.279107140000001</v>
@@ -3517,18 +3516,18 @@
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="76" spans="4:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="4:12" s="2" customFormat="1">
       <c r="D76" s="2" t="s">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="H76" s="2">
         <v>769.13474940000003</v>
@@ -3537,7 +3536,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3550,120 +3549,120 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF4F731-874E-45FE-AA80-8B354D46C2CF}">
   <dimension ref="B3:D46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="2:2" ht="18.75">
+      <c r="B3" s="16" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
-    </row>
-    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
+    <row r="4" spans="2:2" ht="18.75">
+      <c r="B4" s="16"/>
+    </row>
+    <row r="5" spans="2:2" ht="16.5">
+      <c r="B5" s="17" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="19"/>
-    </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
+    <row r="6" spans="2:2" ht="15.75">
+      <c r="B6" s="18"/>
+    </row>
+    <row r="7" spans="2:2" ht="16.5">
+      <c r="B7" s="19" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+    <row r="8" spans="2:2" ht="16.5">
+      <c r="B8" s="17" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
+    <row r="9" spans="2:2" ht="16.5">
+      <c r="B9" s="19" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
+    <row r="10" spans="2:2" ht="16.5">
+      <c r="B10" s="19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="2:2" ht="16.5">
+      <c r="B11" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
+    <row r="12" spans="2:2" ht="16.5">
+      <c r="B12" s="20" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
+    <row r="13" spans="2:2" ht="16.5">
+      <c r="B13" s="19" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
+    <row r="14" spans="2:2" ht="16.5">
+      <c r="B14" s="19" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="20" t="s">
+    <row r="15" spans="2:2" ht="16.5">
+      <c r="B15" s="19" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
+    <row r="16" spans="2:2" ht="16.5">
+      <c r="B16" s="20" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
+    <row r="17" spans="2:3" ht="16.5">
+      <c r="B17" s="19" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+    <row r="18" spans="2:3" ht="17.25">
+      <c r="B18" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="23"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3">
+      <c r="B19" s="22"/>
+    </row>
+    <row r="21" spans="2:3">
       <c r="B21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="24" t="s">
+    <row r="23" spans="2:3">
+      <c r="B23" s="23" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="24"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="23"/>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C25" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
+    <row r="26" spans="2:3">
+      <c r="B26" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3">
       <c r="B27" t="s">
         <v>2</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3">
       <c r="B28" t="s">
         <v>3</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3">
       <c r="B29" t="s">
         <v>4</v>
       </c>
@@ -3687,12 +3686,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+    <row r="32" spans="2:3">
+      <c r="B32" s="23" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4">
       <c r="B34" t="s">
         <v>0</v>
       </c>
@@ -3700,9 +3699,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4">
       <c r="B35" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>211</v>
@@ -3711,87 +3710,87 @@
         <v>215</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4">
       <c r="B36" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4">
       <c r="B37" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4">
       <c r="B38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4">
       <c r="B39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4">
       <c r="B40" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4">
       <c r="B41" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4">
       <c r="B42" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4">
       <c r="B43" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4">
       <c r="B44" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4">
       <c r="B45" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C45" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4">
       <c r="B46" t="s">
         <v>4</v>
       </c>
@@ -3814,6 +3813,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100AC8C87D38434D544A9416DA1AE9C1217" ma:contentTypeVersion="3" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="ee7ee50cfba00ac06777ad9480b5aa35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="552a4e32-e292-4e84-b79f-aefc699ca0de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="847c12b9f1d07d1711c7e51ed32689d2" ns2:_="">
     <xsd:import namespace="552a4e32-e292-4e84-b79f-aefc699ca0de"/>
@@ -3951,52 +3956,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4321C31B-FEA8-48E5-8044-B03A14F31655}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4321C31B-FEA8-48E5-8044-B03A14F31655}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEB976B-F49F-493F-82DD-B59D3053DBEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="552a4e32-e292-4e84-b79f-aefc699ca0de"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88C6B4-595B-49EB-BB0C-4EE3D841E4E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88C6B4-595B-49EB-BB0C-4EE3D841E4E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="552a4e32-e292-4e84-b79f-aefc699ca0de"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEB976B-F49F-493F-82DD-B59D3053DBEE}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
